--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETOR BOMBA OLEO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETOR BOMBA OLEO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RETOR BOMBA OLEO SOLIDEZ TITAN CG150/ XR190-300</t>
+          <t>ROTOR  BOMBA OLEO SOLIDEZ TITAN CG150/ XR190-300</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,17 +464,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RETOR BOMBA OLEO AUDAX BROS NXR160/ TITAN FAN160/ XRE190</t>
+          <t>ROTOR  BOMBA OLEO AUDAX BROS NXR160/ TITAN FAN160/ XRE190</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
     </row>
@@ -495,17 +484,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETOR BOMBA OLEO AUDAX TITAN150 2004 A 2015/ FAN125 2009 A 2018/FAN150 2010/ CRF150F 2012 A 2017/ NXR150 2006 A 2015</t>
+          <t>ROTOR  BOMBA OLEO AUDAX TITAN150 2004 A 2015/ FAN125 2009 A 2018/FAN150 2010/ CRF150F 2012 A 2017/ NXR150 2006 A 2015</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
     </row>
@@ -520,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RETOR BOMBA OLEO EMBUS TITAN FAN150 2004 A 2015/ BROS NXR150 2006 A 2015 11064-E</t>
+          <t>ROTOR  BOMBA OLEO EMBUS TITAN FAN150 2004 A 2015/ BROS NXR150 2006 A 2015 11064-E</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -528,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +524,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETOR BOMBA OLEO SMARTFOX TITAN/ NX/ XR</t>
+          <t>ROTOR  BOMBA OLEO SMARTFOX TITAN/ NX/ XR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -549,7 +532,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
